--- a/artfynd/A 22141-2023 artfynd.xlsx
+++ b/artfynd/A 22141-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125841963</v>
       </c>
       <c r="B2" t="n">
-        <v>58365</v>
+        <v>58366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22141-2023 artfynd.xlsx
+++ b/artfynd/A 22141-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125841963</v>
       </c>
       <c r="B2" t="n">
-        <v>58366</v>
+        <v>58367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22141-2023 artfynd.xlsx
+++ b/artfynd/A 22141-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125841963</v>
       </c>
       <c r="B2" t="n">
-        <v>58367</v>
+        <v>58371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22141-2023 artfynd.xlsx
+++ b/artfynd/A 22141-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125841963</v>
       </c>
       <c r="B2" t="n">
-        <v>58371</v>
+        <v>58374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
